--- a/recipes/recipes.xlsx
+++ b/recipes/recipes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\einav-yehezkely.github.io\recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D158C54B-7C07-46A6-9C45-9AA0BA93DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1124FF0-9215-459A-B7D4-F6B3CBAD5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{855B2972-48CC-4AAB-B0C8-66B655037AB0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="113">
   <si>
     <t>id</t>
   </si>
@@ -366,6 +366,15 @@
   </si>
   <si>
     <t>/recipes/images/10.jpg</t>
+  </si>
+  <si>
+    <t>חרוסת של סבתא אסתר</t>
+  </si>
+  <si>
+    <t>שקדים|אגוזים|ממרח תמרים|מעט קינמון|אפשר מעט מיץ תפוזים</t>
+  </si>
+  <si>
+    <t>קוצצים את השקדים והאגוזים|מערבבים עם ממרח התמרים|מתבלים עם מעט קינמון|מוסיפים מעט מיץ תפוזים</t>
   </si>
 </sst>
 </file>
@@ -751,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37869A0A-AC41-4FF8-85BB-2923FC0BB26B}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
@@ -1246,6 +1255,23 @@
         <v>107</v>
       </c>
     </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/recipes/recipes.xlsx
+++ b/recipes/recipes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\einav\clone_here\einav-yehezkely.github.io\recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1124FF0-9215-459A-B7D4-F6B3CBAD5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC85ADFB-3F38-426A-B894-24C4A0BA6AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{855B2972-48CC-4AAB-B0C8-66B655037AB0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="145">
   <si>
     <t>id</t>
   </si>
@@ -191,18 +191,6 @@
     <t>כוס סוכר עם חצי כוס מים על הגז עד שרותח|שמים 2 חלבונים של הביצים במיקסר ומתחילים לערבל עד שנהיה קצף לבן|מורידים את הסוכר מהגז ומוזגים לאט לאט תוך ערבול החלבונים|לוקחים אוראו דקים ועליהם מזלפים את הקצף|שמים חצי שעה במקרר שיתקשה|מתיכים שוקולד ומוזגים על הקרמבו אחרי שהתקשה|מחזירים למקרר שיתקשה שוב</t>
   </si>
   <si>
-    <t>פנקייק (1)</t>
-  </si>
-  <si>
-    <t>1 כוס קמח|2 כפות סוכר|קורט מלח|2 כפות שמן|1 כוס חלב|2 כפיות אבקת אפייה|2 כפיות תמצית וניל|1 ביצה</t>
-  </si>
-  <si>
-    <t>מערבבים את כל החומרים היבשים בתוך קערה|יוצרים גומה ולתוכה מוסיפים את החלב ביצה טרופה והשמן|בוחשים בעזרת כף עץ עד שאין גושים|ממתינים 5 דקות|יוצקים את התערובת באמצעות מצקת קטנה או כף למחבת טפלון משומנת|לשמן קלות מדי פעם|לטגן על אש בינונית כדקה מכל צד</t>
-  </si>
-  <si>
-    <t>פנקייק (2)</t>
-  </si>
-  <si>
     <t>1 כוס (140 ג’) קמח לבן|1 כפית (5 ג’) אבקת אפיה|1 שקית (10 ג’) סוכר וניל (*אפשר לשים כפית תמצית וניל + כף שטוחה סוכר)|2 כפות (25 ג’) סוכר|1 ביצה|2 כפות שמן (להחליף בחמאה)|1 כוס (240 מ”ל) חלב|קמצוץ מלח|*סירופ מייפל/ שוקולד</t>
   </si>
   <si>
@@ -239,9 +227,6 @@
     <t>עוגת פירות יבשים</t>
   </si>
   <si>
-    <t>לערבב את הסוכר,הביצים והקמח במיקסר|אם יבש מידי אפשר להוסיף כף מים|כשהתערובת מוכנה להוסיף את הפירות ולערבב|להכניס לתנור ב 175 מעלות ללא טורבו קומה 2 בתנור ל27 דקות ולבדוק</t>
-  </si>
-  <si>
     <t>&amp;frac12;1 קמח שיפון|&amp;frac12; כוס קמח שקדים|3 ביצים|3 כפות סוכר חום|1 שקית אבקת אפייה|200-220 גרם פירות יבשים</t>
   </si>
   <si>
@@ -375,6 +360,117 @@
   </si>
   <si>
     <t>קוצצים את השקדים והאגוזים|מערבבים עם ממרח התמרים|מתבלים עם מעט קינמון|מוסיפים מעט מיץ תפוזים</t>
+  </si>
+  <si>
+    <t>פנקייק</t>
+  </si>
+  <si>
+    <t>עוגת ביסקוויטים ואגוזים</t>
+  </si>
+  <si>
+    <t>לקחת מגש עוגה ולשים נייר אפייה|לשים ביסקוויטים על המשטח עד שכל השטח מלא ואז להוסיף עוד כמה|לרסק את הביסקוויטים לחתיכות קטנות (לא לאבקה)|להוסיף 200 גר' חמאה מומסת יחד עם הביסקוויטים לערבב בקערה|לשים את העיסה בתבנית|לקחת כשתי קופסאות של אגוזים שונים (פקאן, קשיו, מלך) ולרסק לחתיכות קטנות|להמיס חפיסת שוקולד חלב ולהוסיף לאגוזים המרוסקים יחד עם קופסת חלב מרוכז וכ־4 כפיות קוקוס ולערבב עד עיסה אחידה|לשפוך את העיסה על המשטח ולהכניס לתנור ב־150 מעלות ל־20 דקות|להוציא ולפזר למעלה קוקוס</t>
+  </si>
+  <si>
+    <t>חלב מרוכז|1 חבילת פתיבר|100 גר' שוקולד חלב|2-2.5 קופסאות של כל מיני אגוזים|קוקוס|200 גר' חמאה</t>
+  </si>
+  <si>
+    <t>/recipes/images/12.jpg</t>
+  </si>
+  <si>
+    <t>עוגיות סבתא שולמית</t>
+  </si>
+  <si>
+    <t>3 כוסות קמח|1 אבקת אפיה|2 סוכר וניל|1 שמנת חמוצה גדולה או 2 קטנות|1 חמאה רכה|&amp;frac34; כוס סוכר לבן</t>
+  </si>
+  <si>
+    <t>ללוש הכל יחד לבצק רך ונעים|לחלק ל-2|לפזר קמח|כל חלק לפתוח במערוך ל- עובי של 1 ס״מ וליצור עיגולים עם כוס זכוכית|לאפות ב־200 מעלות</t>
+  </si>
+  <si>
+    <t>יוצאים 2 מגשי עוגיות</t>
+  </si>
+  <si>
+    <t>/recipes/images/13.jpg</t>
+  </si>
+  <si>
+    <t>/recipes/images/14.jpg</t>
+  </si>
+  <si>
+    <t>סלט סלרי ותפוחי עץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>להכין כמה שעות לפני האוכל</t>
+  </si>
+  <si>
+    <t>סלרי|תפוחים ירוקים|חמוציות|אגוזים|אננס|שמן|לימון</t>
+  </si>
+  <si>
+    <t>סלרי - קצוץ|תפוח - ריבועים קטנים|אגוזים - קצוץ|אננס - קוביות|שמן ולימון - לפי הטעם</t>
+  </si>
+  <si>
+    <t>עוגת קרמבו</t>
+  </si>
+  <si>
+    <t>מסרה את המתכון לימור פרץ המהממת, המשגעת, החכמה, היפה ומתוקה</t>
+  </si>
+  <si>
+    <t>6 ביצים|1 אינסטנט וניל|1 אינסטנט שוקולד|&amp;frac12; כוס סוכר|1 שמנת מתוקה|1 כוס חלב</t>
+  </si>
+  <si>
+    <t>חומרים לקרם שוקולד|3 כפות קקאו|3 כפות סוכר|6 כפות חלב|30 גר' מרגרינה</t>
+  </si>
+  <si>
+    <t>מפרידים את הביצים|מקציפים את החלבונים עם &amp;frac12; כוס סוכר| מוסיפים את החלמונים ואת האינסטנט שוקולד|משמנים תבנית עגולה ומכניסים את התערובת לתנור למשך &amp;frac12; שעה - &amp;frac13; שעה על חום בינוני|אחרי שמוכן לכסות את התבנית במגבת|בשלב השני:|יש להקציף את השמנת+אינסטנט וניל וכוס החלב ולמרוח על גבי המאפה בתבנית|הכנת השלב השלישי:|להמיס את כל החומרים לקרם השוקולד בסיר|אחרי שהקרם מוכן למרוח על גבי קרם השמנת|להכניס למקרר</t>
+  </si>
+  <si>
+    <t>קוגל אילנה</t>
+  </si>
+  <si>
+    <t>לשני מגשים אינגליש קייק</t>
+  </si>
+  <si>
+    <t>400 גר' איטריות בינוניות, &amp;frac12; כוס סוכר|1 כוס צימוקים מושרים במים חמים|3 ביצים|מלח, פלפל - לפי הטעם</t>
+  </si>
+  <si>
+    <t>במחבת|&amp;frac12; כוס סוכר|שמן</t>
+  </si>
+  <si>
+    <t>לבשל ולשמן קצת את האיטריות|לערבב את המצרכים ולשפוך למגשים|לשפוך את מה שנמצא במחבת על הקוגל שבמגשים|לאפות ב־150 מעלות כ־2 שעות|לכסות בנייר כסף מלמעלה</t>
+  </si>
+  <si>
+    <t>מאפינס שיבולת שועל וצימוקים</t>
+  </si>
+  <si>
+    <t>מתאימים להגשה מחוממים עם דבש וחמאה, לארוחת בוקר. החומרים ל־12 יחידות.</t>
+  </si>
+  <si>
+    <t>&amp;frac12; כוס קמח מלא|&amp;frac12; כוס קמח לבן|1 כפית אבקת אפייה|&amp;frac12; כפית מלח|&amp;frac12; כפית סודה לשתייה|1 כוס שיבולת שועל (קוואקר) להכנה מהירה|1 כוס רוויון או שמנת חמוצה|1 ביצה|&amp;frac12; כוס סוכר חום מהודק|&amp;frac12; כוס שמן|&amp;frac34; כוס צימוקים/חמוציות|2-3 בננות בשלות מעוכות במזלג</t>
+  </si>
+  <si>
+    <t>מחממים תנור ל־180 מעלות|בקערה גדולה מערבבים את החומרים היבשים|בקערה נפרדת מערבבים את הקוואקר והרוויון ומעמידים בצד כ־3 דקות|מוסיפים לתערובת הקוואקר את הביצה, הסוכר והשמן ומערבבים היטב|בעזרת כף עץ, מוסיפים את בלילת הקוואקר לחומרים היבשים ומערבבים עד שהקמח נספג|יוצקים לתוך תבנית שקעים משומנת בחמאה, מרגרינה או ממרח לציטין|אופים למשך 18-20 דקות, עד שמזהיבים</t>
+  </si>
+  <si>
+    <t>טירמיסו ללא ביצים</t>
+  </si>
+  <si>
+    <t>מכינים קפה שחור - בקערה רחבה|במיקסר:|מקציפים שמנת מתוקה+אבקת סוכר|להוריד מהירות:|מוסיפים את גבינת המסקרפונה+וניל|לטבול עוגיות בשקוטי בקפה|לסדר בתבנית|להוסיף מעל את התערובת חצי כמות|לטבול עוד בשקוטי ולהניח מעל התערובת (הקרם)|מעל את יתרת הקרם|לכסות בנייר כסף/נצמד למקרר לפחות ל־8 שעות</t>
+  </si>
+  <si>
+    <t>דאל עדשים</t>
+  </si>
+  <si>
+    <t>2 שמנת מתוקה (סה"כ 500 מל')|1 מיכל גבינה מסקרפונה|&amp;frac12; כוס אבקת סוכר|&amp;frac12;1 כוסות קפה שחור (אספרסו) או נס קפה|1 כפות תמצית וניל|2 שרוולים של עוגיות בשקוטי</t>
+  </si>
+  <si>
+    <t>בצל גדול קצוץ|4 שיני שום|שמן זית|2 פחיות עגבניות מרוסקות|&amp;frac12;1 כוסות מים|1 כוס עדשים כתומות שטופות|מלח, פלפל, קארי|1 כפית סילאן טבעי|כוסברה קצוצה</t>
+  </si>
+  <si>
+    <t>מטגנים את הבצל ושיני השום יחד בשמן זית עד שקיפות|מוסיפים את העגבניות המרוסקות והמים|מוסיפים את העדשים הכתומות|מתבלים במלח, פלפל, קארי וכפית סילאן טבעי|מבשלים חצי שעה, בודקים שנשארו מים. אם לא - להוסיף.|מוסיפים כוסברה קצוצה|מבשלים עוד 10 דקות</t>
+  </si>
+  <si>
+    <t>מגישים על אורז</t>
   </si>
 </sst>
 </file>
@@ -760,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37869A0A-AC41-4FF8-85BB-2923FC0BB26B}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
@@ -825,22 +921,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
@@ -848,22 +944,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -871,25 +967,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
@@ -897,22 +993,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
@@ -920,19 +1016,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>109</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
@@ -943,7 +1039,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>23</v>
@@ -963,22 +1059,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
@@ -986,19 +1079,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>82</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
@@ -1006,22 +1102,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
@@ -1029,16 +1125,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>113</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>67</v>
+        <v>115</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
@@ -1046,19 +1148,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>99</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
@@ -1066,25 +1168,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
@@ -1092,19 +1194,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>124</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>126</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
@@ -1112,164 +1220,304 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>131</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>106</v>
+        <v>35</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
